--- a/research/traditional_assets/database/data/tanzania/tanzania_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/tanzania/tanzania_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ6"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.04041500000000001</v>
+        <v>0.166</v>
       </c>
       <c r="E2">
-        <v>0.06369999999999999</v>
+        <v>0.43</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,28 +606,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>210.055</v>
+        <v>327</v>
       </c>
       <c r="L2">
-        <v>0.2891766131141673</v>
+        <v>0.3599339570720969</v>
       </c>
       <c r="M2">
-        <v>54.59999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="N2">
-        <v>0.07069791531788165</v>
+        <v>0.07446808510638298</v>
       </c>
       <c r="O2">
-        <v>0.2599319225917021</v>
+        <v>0.2483180428134557</v>
       </c>
       <c r="P2">
-        <v>54.59999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="Q2">
-        <v>0.07069791531788165</v>
+        <v>0.07446808510638298</v>
       </c>
       <c r="R2">
-        <v>0.2599319225917021</v>
+        <v>0.2483180428134557</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,55 +636,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>353.524</v>
+        <v>358.1</v>
       </c>
       <c r="V2">
-        <v>0.457754758513531</v>
+        <v>0.3284115920763023</v>
       </c>
       <c r="W2">
-        <v>0.1350332225913621</v>
+        <v>0.3148601785211692</v>
       </c>
       <c r="X2">
-        <v>0.08921601045538172</v>
+        <v>0.1535078693527351</v>
       </c>
       <c r="Y2">
-        <v>0.04581721213598042</v>
+        <v>0.1613523091684341</v>
       </c>
       <c r="Z2">
-        <v>0.7435496385586566</v>
+        <v>0.7540044816997262</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.0764132879391575</v>
+        <v>0.1170121839712903</v>
       </c>
       <c r="AC2">
-        <v>-0.0764132879391575</v>
+        <v>-0.1170121839712903</v>
       </c>
       <c r="AD2">
-        <v>521.3199999999999</v>
+        <v>922.5999999999999</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>521.3199999999999</v>
+        <v>922.5999999999999</v>
       </c>
       <c r="AG2">
-        <v>167.7959999999999</v>
+        <v>564.4999999999999</v>
       </c>
       <c r="AH2">
-        <v>0.4029931510026128</v>
+        <v>0.4583209140586189</v>
       </c>
       <c r="AI2">
-        <v>0.3294073044357386</v>
+        <v>0.4202614676809547</v>
       </c>
       <c r="AJ2">
-        <v>0.1784881544012526</v>
+        <v>0.3411082240618767</v>
       </c>
       <c r="AK2">
-        <v>0.13652207023813</v>
+        <v>0.307261049423035</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -701,7 +701,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mwalimu Commercial Bank PLC (DAR:MCB)</t>
+          <t>NMB Bank Plc (DAR:NMB)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,82 +722,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>-0.997</v>
+        <v>173.7</v>
       </c>
       <c r="L3">
-        <v>-0.6270440251572327</v>
+        <v>0.3819261213720316</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>41.5</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.06406298240197593</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>0.2389176741508348</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>41.5</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.06406298240197593</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>0.2389176741508348</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>0.094</v>
+        <v>189.8</v>
       </c>
       <c r="V3">
-        <v>0.007014925373134328</v>
+        <v>0.2929916640938562</v>
       </c>
       <c r="W3">
-        <v>-0.172790294627383</v>
+        <v>0.3133116883116883</v>
       </c>
       <c r="X3">
-        <v>0.07090198047114164</v>
+        <v>0.1218776741923875</v>
       </c>
       <c r="Y3">
-        <v>-0.2436922750985246</v>
+        <v>0.1914340141193009</v>
       </c>
       <c r="Z3">
-        <v>0.286589762076424</v>
+        <v>0.8406654343807766</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.07090198047114164</v>
+        <v>0.1139437128295322</v>
       </c>
       <c r="AC3">
-        <v>-0.07090198047114164</v>
+        <v>-0.1139437128295322</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>200.2</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>200.2</v>
       </c>
       <c r="AG3">
-        <v>-0.094</v>
+        <v>10.39999999999998</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.2360849056603773</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>0.2275517162991589</v>
       </c>
       <c r="AJ3">
-        <v>-0.007064482188486397</v>
+        <v>0.01580066848982069</v>
       </c>
       <c r="AK3">
-        <v>-0.0136508858553587</v>
+        <v>0.01507246376811591</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -814,7 +817,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NMB Bank Plc (DAR:NMB)</t>
+          <t>CRDB Bank Plc (DAR:CRDB)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -822,6 +825,12 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
+      <c r="D4">
+        <v>0.166</v>
+      </c>
+      <c r="E4">
+        <v>0.43</v>
+      </c>
       <c r="G4">
         <v>0</v>
       </c>
@@ -835,28 +844,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>118.2</v>
+        <v>153.3</v>
       </c>
       <c r="L4">
-        <v>0.3257993384785006</v>
+        <v>0.3378884725589597</v>
       </c>
       <c r="M4">
-        <v>29.7</v>
+        <v>39.7</v>
       </c>
       <c r="N4">
-        <v>0.0684331797235023</v>
+        <v>0.08969724356077723</v>
       </c>
       <c r="O4">
-        <v>0.2512690355329949</v>
+        <v>0.258969341161122</v>
       </c>
       <c r="P4">
-        <v>29.7</v>
+        <v>39.7</v>
       </c>
       <c r="Q4">
-        <v>0.0684331797235023</v>
+        <v>0.08969724356077723</v>
       </c>
       <c r="R4">
-        <v>0.2512690355329949</v>
+        <v>0.258969341161122</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -865,301 +874,60 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>205.1</v>
+        <v>168.3</v>
       </c>
       <c r="V4">
-        <v>0.4725806451612903</v>
+        <v>0.3802530501581564</v>
       </c>
       <c r="W4">
-        <v>0.257124211442245</v>
+        <v>0.3164086687306502</v>
       </c>
       <c r="X4">
-        <v>0.0881555928200414</v>
+        <v>0.1851380645130827</v>
       </c>
       <c r="Y4">
-        <v>0.1689686186222036</v>
+        <v>0.1312706042175675</v>
       </c>
       <c r="Z4">
-        <v>0.8810101991257894</v>
+        <v>0.6833860521162826</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.07619580035323602</v>
+        <v>0.1200806551130484</v>
       </c>
       <c r="AC4">
-        <v>-0.07619580035323602</v>
+        <v>-0.1200806551130484</v>
       </c>
       <c r="AD4">
-        <v>191.7</v>
+        <v>722.4</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>191.7</v>
+        <v>722.4</v>
       </c>
       <c r="AG4">
-        <v>-13.40000000000001</v>
+        <v>554.0999999999999</v>
       </c>
       <c r="AH4">
-        <v>0.3063768579191306</v>
+        <v>0.6200858369098712</v>
       </c>
       <c r="AI4">
-        <v>0.2563519657662476</v>
+        <v>0.5491448118586089</v>
       </c>
       <c r="AJ4">
-        <v>-0.03185924869234428</v>
+        <v>0.5559345841276211</v>
       </c>
       <c r="AK4">
-        <v>-0.02469135802469137</v>
+        <v>0.4830020920502092</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Tanzania</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>DCB Commercial Bank Plc (DAR:DCB)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D5">
-        <v>-0.00877</v>
-      </c>
-      <c r="E5">
-        <v>-0.0496</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0.652</v>
-      </c>
-      <c r="L5">
-        <v>0.07325842696629213</v>
-      </c>
-      <c r="M5">
-        <v>-0</v>
-      </c>
-      <c r="N5">
-        <v>-0</v>
-      </c>
-      <c r="O5">
-        <v>-0</v>
-      </c>
-      <c r="P5">
-        <v>-0</v>
-      </c>
-      <c r="Q5">
-        <v>-0</v>
-      </c>
-      <c r="R5">
-        <v>-0</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>1.83</v>
-      </c>
-      <c r="V5">
-        <v>0.244</v>
-      </c>
-      <c r="W5">
-        <v>0.05054263565891473</v>
-      </c>
-      <c r="X5">
-        <v>0.09027642809072202</v>
-      </c>
-      <c r="Y5">
-        <v>-0.03973379243180729</v>
-      </c>
-      <c r="Z5">
-        <v>0.5243313302698245</v>
-      </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
-      <c r="AB5">
-        <v>0.07663077552507898</v>
-      </c>
-      <c r="AC5">
-        <v>-0.07663077552507898</v>
-      </c>
-      <c r="AD5">
-        <v>3.72</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>3.72</v>
-      </c>
-      <c r="AG5">
-        <v>1.89</v>
-      </c>
-      <c r="AH5">
-        <v>0.3315508021390374</v>
-      </c>
-      <c r="AI5">
-        <v>0.2135476463834673</v>
-      </c>
-      <c r="AJ5">
-        <v>0.2012779552715655</v>
-      </c>
-      <c r="AK5">
-        <v>0.1212315586914689</v>
-      </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Tanzania</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>CRDB Bank Plc (DAR:CRDB)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D6">
-        <v>0.08960000000000001</v>
-      </c>
-      <c r="E6">
-        <v>0.177</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>92.2</v>
-      </c>
-      <c r="L6">
-        <v>0.2611158312092892</v>
-      </c>
-      <c r="M6">
-        <v>24.9</v>
-      </c>
-      <c r="N6">
-        <v>0.07844990548204159</v>
-      </c>
-      <c r="O6">
-        <v>0.2700650759219089</v>
-      </c>
-      <c r="P6">
-        <v>24.9</v>
-      </c>
-      <c r="Q6">
-        <v>0.07844990548204159</v>
-      </c>
-      <c r="R6">
-        <v>0.2700650759219089</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>146.5</v>
-      </c>
-      <c r="V6">
-        <v>0.4615626969124134</v>
-      </c>
-      <c r="W6">
-        <v>0.2195238095238095</v>
-      </c>
-      <c r="X6">
-        <v>0.1110094341727218</v>
-      </c>
-      <c r="Y6">
-        <v>0.1085143753510877</v>
-      </c>
-      <c r="Z6">
-        <v>0.6507556210836712</v>
-      </c>
-      <c r="AA6">
-        <v>0</v>
-      </c>
-      <c r="AB6">
-        <v>0.07965552634124237</v>
-      </c>
-      <c r="AC6">
-        <v>-0.07965552634124237</v>
-      </c>
-      <c r="AD6">
-        <v>325.9</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>325.9</v>
-      </c>
-      <c r="AG6">
-        <v>179.4</v>
-      </c>
-      <c r="AH6">
-        <v>0.5066065599253847</v>
-      </c>
-      <c r="AI6">
-        <v>0.402147087857848</v>
-      </c>
-      <c r="AJ6">
-        <v>0.3611111111111111</v>
-      </c>
-      <c r="AK6">
-        <v>0.2702214188883868</v>
-      </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
-      <c r="AM6">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/tanzania/tanzania_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/tanzania/tanzania_bank_money_center.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.166</v>
+        <v>0.194</v>
       </c>
       <c r="E2">
-        <v>0.43</v>
+        <v>0.618</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,28 +606,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>327</v>
+        <v>352.3</v>
       </c>
       <c r="L2">
-        <v>0.3599339570720969</v>
+        <v>0.3656081361560813</v>
       </c>
       <c r="M2">
-        <v>81.2</v>
+        <v>106.5</v>
       </c>
       <c r="N2">
-        <v>0.07446808510638298</v>
+        <v>0.07733081614870753</v>
       </c>
       <c r="O2">
-        <v>0.2483180428134557</v>
+        <v>0.3022991768379222</v>
       </c>
       <c r="P2">
-        <v>81.2</v>
+        <v>106.5</v>
       </c>
       <c r="Q2">
-        <v>0.07446808510638298</v>
+        <v>0.07733081614870753</v>
       </c>
       <c r="R2">
-        <v>0.2483180428134557</v>
+        <v>0.3022991768379222</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,55 +636,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>358.1</v>
+        <v>382</v>
       </c>
       <c r="V2">
-        <v>0.3284115920763023</v>
+        <v>0.2773743828056928</v>
       </c>
       <c r="W2">
-        <v>0.3148601785211692</v>
+        <v>0.2756650216238774</v>
       </c>
       <c r="X2">
-        <v>0.1535078693527351</v>
+        <v>0.1270853980264007</v>
       </c>
       <c r="Y2">
-        <v>0.1613523091684341</v>
+        <v>0.1485796235974767</v>
       </c>
       <c r="Z2">
-        <v>0.7540044816997262</v>
+        <v>0.5249795695995642</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.1170121839712903</v>
+        <v>0.1007866142249892</v>
       </c>
       <c r="AC2">
-        <v>-0.1170121839712903</v>
+        <v>-0.1007866142249892</v>
       </c>
       <c r="AD2">
-        <v>922.5999999999999</v>
+        <v>1251.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>922.5999999999999</v>
+        <v>1251.7</v>
       </c>
       <c r="AG2">
-        <v>564.4999999999999</v>
+        <v>869.7</v>
       </c>
       <c r="AH2">
-        <v>0.4583209140586189</v>
+        <v>0.4761307010536727</v>
       </c>
       <c r="AI2">
-        <v>0.4202614676809547</v>
+        <v>0.4683804819637779</v>
       </c>
       <c r="AJ2">
-        <v>0.3411082240618767</v>
+        <v>0.3870666251279541</v>
       </c>
       <c r="AK2">
-        <v>0.307261049423035</v>
+        <v>0.3797153335661893</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -722,28 +722,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>173.7</v>
+        <v>202.3</v>
       </c>
       <c r="L3">
-        <v>0.3819261213720316</v>
+        <v>0.4053295932678822</v>
       </c>
       <c r="M3">
-        <v>41.5</v>
+        <v>57.2</v>
       </c>
       <c r="N3">
-        <v>0.06406298240197593</v>
+        <v>0.06371129427489419</v>
       </c>
       <c r="O3">
-        <v>0.2389176741508348</v>
+        <v>0.2827483934750371</v>
       </c>
       <c r="P3">
-        <v>41.5</v>
+        <v>57.2</v>
       </c>
       <c r="Q3">
-        <v>0.06406298240197593</v>
+        <v>0.06371129427489419</v>
       </c>
       <c r="R3">
-        <v>0.2389176741508348</v>
+        <v>0.2827483934750371</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -752,55 +752,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>189.8</v>
+        <v>194.3</v>
       </c>
       <c r="V3">
-        <v>0.2929916640938562</v>
+        <v>0.2164179104477612</v>
       </c>
       <c r="W3">
-        <v>0.3133116883116883</v>
+        <v>0.2984215961056203</v>
       </c>
       <c r="X3">
-        <v>0.1218776741923875</v>
+        <v>0.1045549296930784</v>
       </c>
       <c r="Y3">
-        <v>0.1914340141193009</v>
+        <v>0.1938666664125419</v>
       </c>
       <c r="Z3">
-        <v>0.8406654343807766</v>
+        <v>0.7251198605259336</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.1139437128295322</v>
+        <v>0.09664950963286315</v>
       </c>
       <c r="AC3">
-        <v>-0.1139437128295322</v>
+        <v>-0.09664950963286315</v>
       </c>
       <c r="AD3">
-        <v>200.2</v>
+        <v>411.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>200.2</v>
+        <v>411.8</v>
       </c>
       <c r="AG3">
-        <v>10.39999999999998</v>
+        <v>217.5</v>
       </c>
       <c r="AH3">
-        <v>0.2360849056603773</v>
+        <v>0.3144471594379964</v>
       </c>
       <c r="AI3">
-        <v>0.2275517162991589</v>
+        <v>0.346399730820996</v>
       </c>
       <c r="AJ3">
-        <v>0.01580066848982069</v>
+        <v>0.1950147942257689</v>
       </c>
       <c r="AK3">
-        <v>0.01507246376811591</v>
+        <v>0.2187028657616893</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.166</v>
+        <v>0.194</v>
       </c>
       <c r="E4">
-        <v>0.43</v>
+        <v>0.618</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -844,28 +844,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>153.3</v>
+        <v>150</v>
       </c>
       <c r="L4">
-        <v>0.3378884725589597</v>
+        <v>0.3229278794402584</v>
       </c>
       <c r="M4">
-        <v>39.7</v>
+        <v>49.3</v>
       </c>
       <c r="N4">
-        <v>0.08969724356077723</v>
+        <v>0.1028368794326241</v>
       </c>
       <c r="O4">
-        <v>0.258969341161122</v>
+        <v>0.3286666666666667</v>
       </c>
       <c r="P4">
-        <v>39.7</v>
+        <v>49.3</v>
       </c>
       <c r="Q4">
-        <v>0.08969724356077723</v>
+        <v>0.1028368794326241</v>
       </c>
       <c r="R4">
-        <v>0.258969341161122</v>
+        <v>0.3286666666666667</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -874,55 +874,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>168.3</v>
+        <v>187.7</v>
       </c>
       <c r="V4">
-        <v>0.3802530501581564</v>
+        <v>0.3915310805173133</v>
       </c>
       <c r="W4">
-        <v>0.3164086687306502</v>
+        <v>0.2529084471421346</v>
       </c>
       <c r="X4">
-        <v>0.1851380645130827</v>
+        <v>0.1496158663597231</v>
       </c>
       <c r="Y4">
-        <v>0.1312706042175675</v>
+        <v>0.1032925807824115</v>
       </c>
       <c r="Z4">
-        <v>0.6833860521162826</v>
+        <v>0.4048988842398884</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.1200806551130484</v>
+        <v>0.1049237188171152</v>
       </c>
       <c r="AC4">
-        <v>-0.1200806551130484</v>
+        <v>-0.1049237188171152</v>
       </c>
       <c r="AD4">
-        <v>722.4</v>
+        <v>839.9</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>722.4</v>
+        <v>839.9</v>
       </c>
       <c r="AG4">
-        <v>554.0999999999999</v>
+        <v>652.2</v>
       </c>
       <c r="AH4">
-        <v>0.6200858369098712</v>
+        <v>0.6366254832107936</v>
       </c>
       <c r="AI4">
-        <v>0.5491448118586089</v>
+        <v>0.5661229441898086</v>
       </c>
       <c r="AJ4">
-        <v>0.5559345841276211</v>
+        <v>0.5763520678685049</v>
       </c>
       <c r="AK4">
-        <v>0.4830020920502092</v>
+        <v>0.5032795740412069</v>
       </c>
       <c r="AL4">
         <v>0</v>
